--- a/docs/PRAP_Development_Plan_v2.72.xlsx
+++ b/docs/PRAP_Development_Plan_v2.72.xlsx
@@ -7769,7 +7769,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>R-62, REQ-DSH-20: AN ISSUE A MANAGER HAS REVIEWED IS SHOWN AS REVIEWED. Asked for from the field: a month short of its standard, over it or with nobody on it may be a decision rather than a problem - 'over in the run-up to the interim lock, the sponsor is paying for it' - and drawing those in the same alarm colour as the ones nobody has examined hides the real alarms among them. A new sheet, IssueReview (project_id, month, issue, status, gap_fte, rationale, reviewed_by, reviewed_at), holds one review per project, month and issue; source schema steps 15 to 16. CLICKING AN ISSUE MONTH in Resource by project, or its row in the Standard vs staffed list, opens the month with a Manager review box: a decision ('Confirmed - no issue', 'Accepted', 'To be fixed'), who confirmed it, the reason, and 'Apply to the whole run' for the consecutive months carrying the same issue - or 'Open the project' to change the data instead. The first two CLOSE the issue and need a reason; 'To be fixed' keeps it open with a note. A closed month STAYS MARKED BUT IS DRAWN MUTED, gray, and clicking it shows the decision, who made it, when and why, which can be changed or removed at any time. The counts on the control, the tile and the list are OPEN issues, with the reviewed ones counted apart ('2 reviewed'); the list filters Any review / Open / Reviewed and sorts open issues first, and Show in Resource by project gains 'Reviewed and closed'. A REVIEW COVERS THE FIGURES IT WAS MADE ON: gap_fte records the gap reviewed, and if the month's gap moves, the review no longer closes it - the month is open again, marked 're-check' - and V-40 (new, information) says so; a review of an issue that has gone is kept as history and V-40 says that too. A review is an edit like any other: held until Save, in the change log, exported and read back, and judged identically by the Python reference. A workbook from before schema 16 opens with no reviews (V-09 information). No figure moves; template v1.20, examples v1.22 and v1.14, the small one carrying two accepted months and one to be fixed. Clicking an issue month used to fold its project row open or shut instead - the row's own click came first - and that is fixed. tools/test_review.py is new: 47 checks, four proved by putting the fault back.</t>
+          <t>R-62, REQ-DSH-20: AN ISSUE A MANAGER HAS REVIEWED IS SHOWN AS REVIEWED. Asked for from the field: a month short of its standard, over it or with nobody on it may be a decision rather than a problem - 'over in the run-up to the interim lock, the sponsor is paying for it' - and drawing those in the same alarm colour as the ones nobody has examined hides the real alarms among them. A new sheet, IssueReview (project_id, month, issue, status, gap_fte, rationale, reviewed_by, reviewed_at), holds one review per project, month and issue; source schema steps 15 to 16. CLICKING AN ISSUE MONTH in Resource by project, or its row in the Standard vs staffed list, opens the month with a Manager review box: a decision ('Confirmed - no issue', 'Accepted', 'To be fixed'), who confirmed it, the reason, and 'Apply to the whole run' for the consecutive months carrying the same issue - or 'Open the project' to change the data instead. The first two CLOSE the issue and need a reason; 'To be fixed' keeps it open with a note. A closed month STAYS MARKED BUT IS DRAWN MUTED, gray, and clicking it shows the decision, who made it, when and why, which can be changed or removed at any time. The counts on the control, the tile and the list are OPEN issues, with the reviewed ones counted apart ('2 reviewed'); the list filters Any review / Open / Reviewed and sorts open issues first, and Show in Resource by project gains 'Reviewed and closed'. A REVIEW COVERS THE FIGURES IT WAS MADE ON: gap_fte records the gap reviewed, and if the month's gap moves, the review no longer closes it - the month is open again, marked 're-check' - and V-40 (new, information) says so; a review of an issue that has gone is kept as history and V-40 says that too. A review is an edit like any other: held until Save, in the change log, exported and read back, and judged identically by the Python reference. A workbook from before schema 16 opens with no reviews (V-09 information). No figure moves; template v1.20, examples v1.22 and v1.14, the small one carrying two accepted months and one to be fixed. Clicking an issue month used to fold its project row open or shut instead - the row's own click came first - and that is fixed. THE STANDARD VS STAFFED LIST IS IN ORDER OF PROJECT ID, THEN MONTH, both ascending (asked for straight after), and lists every month: it was largest gap first and capped at 40, which in project order would have cut whole projects off the end. tools/test_review.py is new: 49 checks, five proved by putting the fault back.</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">

--- a/docs/PRAP_Development_Plan_v2.72.xlsx
+++ b/docs/PRAP_Development_Plan_v2.72.xlsx
@@ -3740,7 +3740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4700,22 +4700,22 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>R-62</t>
+          <t>R-63</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Python edition</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Let a manager confirm a short / over / not-staffed issue - 'no issue' or 'accepted', with a rationale - from the issue itself, changeable later; show confirmed issues distinguished (muted) but still readable, with the confirmation and rationale shown whenever the issue is clicked.</t>
+          <t>Make the file search windows more graphical and useful; do not apply the session time-out to a private plan; when a session does time out, say so in a pop-up.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Applied. New sheet IssueReview; source schema steps 15 to 16. Clicking an issue month opens it with a Manager review box (decision, manager, reason, whole run); Confirmed and Accepted close it and need a reason, To be fixed keeps it open. Closed months are drawn muted, counted apart, and filterable. A review covers the gap it was made at; V-40 added; REQ-DSH-20 added; no figure moves.</t>
+          <t>Applied (Python edition 1.35; desktop plan v1.18). A plan in My plans takes no hold, so it never times out (NR-STO-20). A lapsed hold on a team plan raises a pop-up naming who took over and offering to keep your version (NR-STO-21). The file window gains places, a clickable path with back/forward/up, type badges, how-long-ago and date groups, a filter, list or tiles, details, the keyboard, and who saved / is editing a plan (NR-IMP-10).</t>
         </is>
       </c>
       <c r="E47" s="17" t="inlineStr">
@@ -4727,22 +4727,22 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>R-61</t>
+          <t>R-62</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>Let a user whose session timed out save the working plan into their personal folder.</t>
+          <t>Let a manager confirm a short / over / not-staffed issue - 'no issue' or 'accepted', with a rationale - from the issue itself, changeable later; show confirmed issues distinguished (muted) but still readable, with the confirmation and rationale shown whenever the issue is clicked.</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Applied (Python edition). When the shared plan can no longer be written - the hold lapsed and was taken over, or a colleague saved since it was opened - a bar offers 'Save my version to My plans': a new, uniquely named file in the person's own folder, after which the window works on it. Also on the File menu. The team's plan is never touched.</t>
+          <t>Applied. New sheet IssueReview; source schema steps 15 to 16. Clicking an issue month opens it with a Manager review box (decision, manager, reason, whole run); Confirmed and Accepted close it and need a reason, To be fixed keeps it open. Closed months are drawn muted, counted apart, and filterable. A review covers the gap it was made at; V-40 added; REQ-DSH-20 added; no figure moves.</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
@@ -4754,22 +4754,22 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>R-60</t>
+          <t>R-61</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Data model</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Colour every project's periods from an assumption on the General assumptions tab; where none is assumed for a period, let the project choose.</t>
+          <t>Let a user whose session timed out save the working plan into their personal folder.</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Applied. New sheet PeriodHighlight, one default colour per period name; source schema steps 14 to 15. The project's own Highlight wins, then the default, then gray; derived periods take the default too. Shipped defaults restore the O-10 reading as data. V-39 added; REQ-PRJ-16 added; no figure moves.</t>
+          <t>Applied (Python edition). When the shared plan can no longer be written - the hold lapsed and was taken over, or a colleague saved since it was opened - a bar offers 'Save my version to My plans': a new, uniquely named file in the person's own folder, after which the window works on it. Also on the File menu. The team's plan is never touched.</t>
         </is>
       </c>
       <c r="E49" s="17" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>R-59</t>
+          <t>R-60</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>Add a Highlight column to Periods like the Milestones one: choose the colour of each project's period, gray when none is chosen.</t>
+          <t>Colour every project's periods from an assumption on the General assumptions tab; where none is assumed for a period, let the project choose.</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Applied. ProjectPeriod gains period_highlight after period_end; source schema steps 13 to 14. Its own list of the same five colours; the colour word inside the value is what is read. Unmarked periods are gray, shaded by weight, superseding the per-period-name hues of O-10. A value naming no colour is V-38. REQ-PRJ-15 added; no figure moves.</t>
+          <t>Applied. New sheet PeriodHighlight, one default colour per period name; source schema steps 14 to 15. The project's own Highlight wins, then the default, then gray; derived periods take the default too. Shipped defaults restore the O-10 reading as data. V-39 added; REQ-PRJ-16 added; no figure moves.</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
@@ -4808,22 +4808,22 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>R-58</t>
+          <t>R-59</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Audit</t>
+          <t>Data model</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Saving shows 'the change log could not be written to the audit folder ... Failed to fetch' - is the audit trail working?</t>
+          <t>Add a Highlight column to Periods like the Milestones one: choose the colour of each project's period, gray when none is chosen.</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>It works; the Python application behind the window had stopped. Its watchdog gave up after fifteen minutes without a heartbeat, which a sleeping browser tab or laptop reaches. Now only the page closing stops it, and a window whose application has stopped says so and offers downloads of the plan and the unarchived change log.</t>
+          <t>Applied. ProjectPeriod gains period_highlight after period_end; source schema steps 13 to 14. Its own list of the same five colours; the colour word inside the value is what is read. Unmarked periods are gray, shaded by weight, superseding the per-period-name hues of O-10. A value naming no colour is V-38. REQ-PRJ-15 added; no figure moves.</t>
         </is>
       </c>
       <c r="E51" s="17" t="inlineStr">
@@ -4835,22 +4835,22 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>R-57</t>
+          <t>R-58</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Audit</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>The import file window does not show the sub-folders of a level-1 folder.</t>
+          <t>Saving shows 'the change log could not be written to the audit folder ... Failed to fetch' - is the audit trail working?</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Fixed in the Python edition. A double-click opened the folder on its first click and then the row under the pointer in the redrawn list on its second, so the folder asked for was skipped. The second click of a sequence is now ignored on a freshly drawn list, and a double-click chooses only the row it began on.</t>
+          <t>It works; the Python application behind the window had stopped. Its watchdog gave up after fifteen minutes without a heartbeat, which a sleeping browser tab or laptop reaches. Now only the page closing stops it, and a window whose application has stopped says so and offers downloads of the plan and the unarchived change log.</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>R-56</t>
+          <t>R-57</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Filters by name; a new project or person stays selected after Save; Resource by project to show auto vs manual, to filter to problem projects, and to count not-staffed months; file dates when importing and exporting.</t>
+          <t>The import file window does not show the sub-folders of a level-1 folder.</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Applied. Project and Person filters list names with a search box. A row added with + row is the selection through typing, Save and a change of identifier. Resource by project gains an estimation pill per project, a mark on stated months and a Show control (issues, short, over, not staffed, stated by hand); not-staffed months are counted on the control, the tile and the Standard vs staffed list. The Python file browser shows modified dates, newest first; exported names carry date and time.</t>
+          <t>Fixed in the Python edition. A double-click opened the folder on its first click and then the row under the pointer in the redrawn list on its second, so the folder asked for was skipped. The second click of a sequence is now ignored on a freshly drawn list, and a double-click chooses only the row it began on.</t>
         </is>
       </c>
       <c r="E53" s="17" t="inlineStr">
@@ -4889,22 +4889,22 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>R-55</t>
+          <t>R-56</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>Make the calculated-FTE export usable for analysis outside the application, including by an AI: which projects are short or over, and by how much.</t>
+          <t>Filters by name; a new project or person stays selected after Save; Resource by project to show auto vs manual, to filter to problem projects, and to count not-staffed months; file dates when importing and exporting.</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>Applied. ProjectMonth gains demand_fte, staffed_fte, gap_fte and gap_dir, and a row for every month nobody is on (V-36), which used to be dropped. Flags gains project runs - short, over, unallocated - and Summary the matching totals. The gap is the project's own whatever filter is on. PersonMonth gains the months a person is employed and on nothing, as spare capacity. REQ-OUT-06 amended. Alongside: tools/prap_analyze.py (scorecard and what-if comparison) and docs/PRAP_AI_Analysis_Guide.md.</t>
+          <t>Applied. Project and Person filters list names with a search box. A row added with + row is the selection through typing, Save and a change of identifier. Resource by project gains an estimation pill per project, a mark on stated months and a Show control (issues, short, over, not staffed, stated by hand); not-staffed months are counted on the control, the tile and the Standard vs staffed list. The Python file browser shows modified dates, newest first; exported names carry date and time.</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
@@ -4916,22 +4916,22 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>R-54</t>
+          <t>R-55</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Output</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Two raised from the screen: three cell marks were printing their own CSS escape, and the Order column on Milestones is not wanted.</t>
+          <t>Make the calculated-FTE export usable for analysis outside the application, including by an AI: which projects are short or over, and by how much.</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Both applied. The marks were written with a doubled backslash, so \25B2, \25BC and \26A0 were drawn as text instead of the arrows and the warning sign; three guards added, one static and two on the rendered character. milestone_seq is no longer drawn - it orders nothing, and its pop-up said otherwise. period_seq is kept: both engines sort by it and V-18 reports a duplicate as an error.</t>
+          <t>Applied. ProjectMonth gains demand_fte, staffed_fte, gap_fte and gap_dir, and a row for every month nobody is on (V-36), which used to be dropped. Flags gains project runs - short, over, unallocated - and Summary the matching totals. The gap is the project's own whatever filter is on. PersonMonth gains the months a person is employed and on nothing, as spare capacity. REQ-OUT-06 amended. Alongside: tools/prap_analyze.py (scorecard and what-if comparison) and docs/PRAP_AI_Analysis_Guide.md.</t>
         </is>
       </c>
       <c r="E55" s="17" t="inlineStr">
@@ -4943,7 +4943,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>R-53</t>
+          <t>R-54</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>Let the Standard vs staffed list be narrowed, and keep a project's identity on screen while its table scrolls sideways.</t>
+          <t>Two raised from the screen: three cell marks were printing their own CSS escape, and the Order column on Milestones is not wanted.</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>Both applied. The list gains three controls - direction, project, smallest gap - which narrow the LIST only; the tile and the control in the panel head go on counting everything, because they are the alarm. The Project table freezes the row handle, project_id and project_name at its left edge. REQ-DSH-15 amended and REQ-DSH-19 added.</t>
+          <t>Both applied. The marks were written with a doubled backslash, so \25B2, \25BC and \26A0 were drawn as text instead of the arrows and the warning sign; three guards added, one static and two on the rendered character. milestone_seq is no longer drawn - it orders nothing, and its pop-up said otherwise. period_seq is kept: both engines sort by it and V-18 reports a duplicate as an error.</t>
         </is>
       </c>
       <c r="E56" s="17" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>R-52</t>
+          <t>R-53</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Move Standard vs staffed onto Resource by project and open it from a control there.</t>
+          <t>Let the Standard vs staffed list be narrowed, and keep a project's identity on screen while its table scrolls sideways.</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Applied. The list is now a dialog opened from that panel's head; a row opens the month on top of it. What the move costs - a list behind a click - is paid back by the control, which states how many months are off their standard and in which direction instead of naming the screen. REQ-DSH-15 amended. It also exposed a defect of its own: the tile that was supposed to jump to the old panel had never worked, because the pop-up handler runs in the capture phase and swallowed the click on a div that declares role=button.</t>
+          <t>Both applied. The list gains three controls - direction, project, smallest gap - which narrow the LIST only; the tile and the control in the panel head go on counting everything, because they are the alarm. The Project table freezes the row handle, project_id and project_name at its left edge. REQ-DSH-15 amended and REQ-DSH-19 added.</t>
         </is>
       </c>
       <c r="E57" s="17" t="inlineStr">
@@ -4997,7 +4997,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>R-51</t>
+          <t>R-52</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>Give every section a control that opens it full screen, so wide tables can be read and typed into at the size they actually are.</t>
+          <t>Move Standard vs staffed onto Resource by project and open it from a control there.</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Applied. The panel is drawn against the viewport rather than moved into an overlay or a dialog - an edit re-renders the pane it lives in, so a detached node would be orphaned by the first keystroke saved, and a modal would make Save inert. The sticky band carrying Save and the tabs is lifted above the section instead of being covered. Panels gained names so the state survives a re-render and a change of selected row. REQ-DSH-18 added.</t>
+          <t>Applied. The list is now a dialog opened from that panel's head; a row opens the month on top of it. What the move costs - a list behind a click - is paid back by the control, which states how many months are off their standard and in which direction instead of naming the screen. REQ-DSH-15 amended. It also exposed a defect of its own: the tile that was supposed to jump to the old panel had never worked, because the pop-up handler runs in the capture phase and swallowed the click on a div that declares role=button.</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
@@ -5024,22 +5024,22 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>R-50</t>
+          <t>R-51</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Data model</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Mark a milestone in a colour, and carry the mark to the Project timeline on both tabs.</t>
+          <t>Give every section a control that opens it full screen, so wide tables can be read and typed into at the size they actually are.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Applied. Milestone gains milestone_highlight beside milestone_date; source schema steps 12 to 13. The colours live in Lists, and the application reads the COLOUR WORD inside the value - so a team may write what their colour means and keep both. A value with no colour word in it is V-37 and the milestone draws unmarked. REQ-PRJ-14 added.</t>
+          <t>Applied. The panel is drawn against the viewport rather than moved into an overlay or a dialog - an edit re-renders the pane it lives in, so a detached node would be orphaned by the first keystroke saved, and a modal would make Save inert. The sticky band carrying Save and the tabs is lifted above the section instead of being covered. Panels gained names so the state survives a re-render and a change of selected row. REQ-DSH-18 added.</t>
         </is>
       </c>
       <c r="E59" s="17" t="inlineStr">
@@ -5051,7 +5051,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-50</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>Add 'Inspection' as a standard milestone.</t>
+          <t>Mark a milestone in a colour, and carry the mark to the Project timeline on both tabs.</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Applied. Milestone list grows to ten. Unlike the others, 'Inspection' MAY REPEAT within one project, so REQ-PRJ-13 and V-20 were added and V-14's uniqueness check now exempts it.</t>
+          <t>Applied. Milestone gains milestone_highlight beside milestone_date; source schema steps 12 to 13. The colours live in Lists, and the application reads the COLOUR WORD inside the value - so a team may write what their colour means and keep both. A value with no colour word in it is V-37 and the milestone draws unmarked. REQ-PRJ-14 added.</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
@@ -5078,22 +5078,22 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Calculation</t>
+          <t>Data model</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Sheet 05 derivation edits: Before-Start-up ends at 'Protocol (v1)'; Start-up begins the day after it and ends at 'First SIV' (or 'FPI'); a seventh period 'After Close-out (final)' spans the Inspection dates.</t>
+          <t>Add 'Inspection' as a standard milestone.</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Applied. Clinical period set grows to six names; REQ-PRJ-12 and REQ-CAL-09 reworded; REQ-CAL-13 added for the milestone-beats-offset rule; 'FPI' restored to the milestone list as the First SIV fallback.</t>
+          <t>Applied. Milestone list grows to ten. Unlike the others, 'Inspection' MAY REPEAT within one project, so REQ-PRJ-13 and V-20 were added and V-14's uniqueness check now exempts it.</t>
         </is>
       </c>
       <c r="E61" s="17" t="inlineStr">
@@ -5105,7 +5105,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -5115,66 +5115,66 @@
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>Not requested - found while applying R-02.</t>
+          <t>Sheet 05 derivation edits: Before-Start-up ends at 'Protocol (v1)'; Start-up begins the day after it and ends at 'First SIV' (or 'FPI'); a seventh period 'After Close-out (final)' spans the Inspection dates.</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Period 7 was defined as earliest to latest 'Inspection'. Where an inspection is dated on or before the final DB lock, that makes period 7 start before period 6 and overlap Conduct. Only inspections AFTER the final DB lock open period 7; earlier ones stay markers, reported by V-21. CONFIRMED by the reviewer at the v1.1 review.</t>
+          <t>Applied. Clinical period set grows to six names; REQ-PRJ-12 and REQ-CAL-09 reworded; REQ-CAL-13 added for the milestone-beats-offset rule; 'FPI' restored to the milestone list as the First SIV fallback.</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>Applied</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>R-13</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Calculation</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Two requests at the component-list v0.7 review: highlight the interim and final DB lock milestones in red, and add a project utilisation graph to the 'Source data (project)' tab.</t>
+          <t>Not requested - found while applying R-02.</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Both applied. The DB locks are the milestones the whole period derivation hangs on - move a lock and every period after it moves - so red plus a larger marker is warranted; size carries it as well as hue, because D-04 makes 'never colour alone' a floor. The cut-off milestones stay ordinary: the cut-off is preparation, the lock is the event. The utilisation graph needed a new requirement, REQ-DSH-12, because the person tab's equivalent rests on absolute thresholds a project does not have - which the reviewer identified. The references are therefore relative: 2x and 0.5x the portfolio average for an active project-month, plus the project's own lifetime average.</t>
+          <t>Period 7 was defined as earliest to latest 'Inspection'. Where an inspection is dated on or before the final DB lock, that makes period 7 start before period 6 and overlap Conduct. Only inspections AFTER the final DB lock open period 7; earlier ones stay markers, reported by V-21. CONFIRMED by the reviewer at the v1.1 review.</t>
         </is>
       </c>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>R-12</t>
+          <t>R-13</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>Raised as a question about the PersonPeriodWeight key - why is period_start needed when assignment_id looks unique?</t>
+          <t>Two requests at the component-list v0.7 review: highlight the interim and final DB lock milestones in red, and add a project utilisation graph to the 'Source data (project)' tab.</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>The key is correct and unchanged: (assignment_id, period_start). assignment_id is unique in Assignment, but PersonPeriodWeight is a CHILD of it, and REQ-PSN-05, V-06 and the data model all allow one assignment to carry several non-overlapping override windows. Keying on assignment_id alone would cap it at one. But checking the question exposed two real gaps, both now closed: V-06's assignment-window half had never been implemented, so an overlapping pair passed silently and the applied weight depended on row order; and nothing checked that a PersonPeriodWeight row referred to a real assignment, so an orphan override was accepted and ignored without a word. V-24 added for the second. The dummy fixture now carries an assignment with TWO windows - it only ever had one each, which is why neither gap surfaced.</t>
+          <t>Both applied. The DB locks are the milestones the whole period derivation hangs on - move a lock and every period after it moves - so red plus a larger marker is warranted; size carries it as well as hue, because D-04 makes 'never colour alone' a floor. The cut-off milestones stay ordinary: the cut-off is preparation, the lock is the event. The utilisation graph needed a new requirement, REQ-DSH-12, because the person tab's equivalent rests on absolute thresholds a project does not have - which the reviewer identified. The references are therefore relative: 2x and 0.5x the portfolio average for an active project-month, plus the project's own lifetime average.</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
@@ -5186,22 +5186,22 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>R-11</t>
+          <t>R-12</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Data model</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Name the two conduct stretches apart - 'Conduct (interim)' before an interim DB lock, 'Conduct (final)' after it or where there is no interim lock - and key ProjectPeriod on (project_id, period_name).</t>
+          <t>Raised as a question about the PersonPeriodWeight key - why is period_start needed when assignment_id looks unique?</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Applied, and it simplifies more than it costs. The clinical period set grows from six names to seven, but no name now repeats in a project, so ProjectPeriod has a natural key again and period_seq goes back to carrying order rather than identity. V-18 becomes a plain uniqueness check. REQ-CAL-11 and REQ-PRJ-12 reworded. REQ-DSH-10, which existed to number repeated names on screen, is now satisfied by the data model instead - the display numbering is kept only as a guard. This is the alternative offered against decision D-15 at the component-list review, so D-15 is superseded. Schema 4 -&gt; 5: the columns are unchanged but the period_name value set is not, so a v4 file's 'Conduct' rows would fail V-15. PeriodWeightStandard grows 48 -&gt; 56 rows and RoleFactor 249 -&gt; 289; both new Conduct entries carry the same weights the single 'Conduct' did, so the change renames without reweighting - the dummy dataset returns byte-identical load figures.</t>
+          <t>The key is correct and unchanged: (assignment_id, period_start). assignment_id is unique in Assignment, but PersonPeriodWeight is a CHILD of it, and REQ-PSN-05, V-06 and the data model all allow one assignment to carry several non-overlapping override windows. Keying on assignment_id alone would cap it at one. But checking the question exposed two real gaps, both now closed: V-06's assignment-window half had never been implemented, so an overlapping pair passed silently and the applied weight depended on row order; and nothing checked that a PersonPeriodWeight row referred to a real assignment, so an orphan override was accepted and ignored without a word. V-24 added for the second. The dummy fixture now carries an assignment with TWO windows - it only ever had one each, which is why neither gap surfaced.</t>
         </is>
       </c>
       <c r="E65" s="17" t="inlineStr">
@@ -5213,7 +5213,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-11</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>The role factor must be given by role AND project type AND clinical phase AND period, not by role and type alone.</t>
+          <t>Name the two conduct stretches apart - 'Conduct (interim)' before an interim DB lock, 'Conduct (final)' after it or where there is no interim lock - and key ProjectPeriod on (project_id, period_name).</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Applied. RoleFactor gains clinical_phase and period_name; its key becomes all four columns and the sheet grows from 13 rows to 249. REQ-CAL-02 reworded, V-23 added, schema 3 -&gt; 4. This is a real gain in expressiveness - a role's burden genuinely is not flat across a project, and the dummy data now shows the database programmer peaking at start-up and the analyst at lock. It carries two costs, both stated rather than hidden: 249 rows is a large hand-maintained table, and RoleFactor now varies over the same three dimensions as PeriodWeightStandard, so the two multiply and can double-count if both are edited for the same reason. See the note on sheet 04.</t>
+          <t>Applied, and it simplifies more than it costs. The clinical period set grows from six names to seven, but no name now repeats in a project, so ProjectPeriod has a natural key again and period_seq goes back to carrying order rather than identity. V-18 becomes a plain uniqueness check. REQ-CAL-11 and REQ-PRJ-12 reworded. REQ-DSH-10, which existed to number repeated names on screen, is now satisfied by the data model instead - the display numbering is kept only as a guard. This is the alternative offered against decision D-15 at the component-list review, so D-15 is superseded. Schema 4 -&gt; 5: the columns are unchanged but the period_name value set is not, so a v4 file's 'Conduct' rows would fail V-15. PeriodWeightStandard grows 48 -&gt; 56 rows and RoleFactor 249 -&gt; 289; both new Conduct entries carry the same weights the single 'Conduct' did, so the change renames without reweighting - the dummy dataset returns byte-identical load figures.</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
@@ -5240,22 +5240,22 @@
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-10</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Data model</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Nine components changed at the component-list v0.3 review: a fourth tab for the standing assumptions, insert-row on every editable table, clinical-phase filter, the unit toggle demoted from filter to setting, the demand-chart legend replaced by a hover pop-up, four timeline changes, a time zone on the load stamp, and the edit counter stating its validation standing.</t>
+          <t>The role factor must be given by role AND project type AND clinical phase AND period, not by role and type alone.</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Applied. Seven were satisfiable by design alone. Two were not: nothing in the plan required the assumptions to be reachable in the application, and nothing said a row could be created at all - so REQ-DSH-11 and REQ-IMP-11 were added. REQ-DSH-05 and REQ-IMP-05 reworded. One conflict surfaced: O-10 asks the timeline to be coloured by period name, which contradicts accepted decision D-06 (shade by weight). O-10 is the more specific instruction, so D-06 is superseded and weight becomes a lightness step within each period hue.</t>
+          <t>Applied. RoleFactor gains clinical_phase and period_name; its key becomes all four columns and the sheet grows from 13 rows to 249. REQ-CAL-02 reworded, V-23 added, schema 3 -&gt; 4. This is a real gain in expressiveness - a role's burden genuinely is not flat across a project, and the dummy data now shows the database programmer peaking at start-up and the analyst at lock. It carries two costs, both stated rather than hidden: 249 rows is a large hand-maintained table, and RoleFactor now varies over the same three dimensions as PeriodWeightStandard, so the two multiply and can double-count if both are edited for the same reason. See the note on sheet 04.</t>
         </is>
       </c>
       <c r="E67" s="17" t="inlineStr">
@@ -5267,7 +5267,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>R-08</t>
+          <t>R-09</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>The two 'Conduct' stretches of a project must be distinguishable on screen (S2-04).</t>
+          <t>Nine components changed at the component-list v0.3 review: a fourth tab for the standing assumptions, insert-row on every editable table, clinical-phase filter, the unit toggle demoted from filter to setting, the demand-chart legend replaced by a hover pop-up, four timeline changes, a time zone on the load stamp, and the edit counter stating its validation standing.</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Applied as REQ-DSH-10. A display rule, not a data change: period_name stays 'Conduct' in the workbook and the screen shows it with its sequence, 'Conduct (1)' and 'Conduct (2)'. Changing the stored name would have broken the weight lookup and V-15.</t>
+          <t>Applied. Seven were satisfiable by design alone. Two were not: nothing in the plan required the assumptions to be reachable in the application, and nothing said a row could be created at all - so REQ-DSH-11 and REQ-IMP-11 were added. REQ-DSH-05 and REQ-IMP-05 reworded. One conflict surfaced: O-10 asks the timeline to be coloured by period name, which contradicts accepted decision D-06 (shade by weight). O-10 is the more specific instruction, so D-06 is superseded and weight becomes a lightness step within each period hue.</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
@@ -5294,22 +5294,22 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-08</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Calculation</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Thresholds stay ABSOLUTE, not relative to capacity_fte (S2-01), and the under-allocation floor moves to 0.60 FTE (S2-05).</t>
+          <t>The two 'Conduct' stretches of a project must be distinguishable on screen (S2-04).</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Applied. Taken together these resolve the defect S2-01 was raised about: at a 0.60 floor every capacity in the data can clear it - 1.00 needs 60% utilisation, 0.80 needs 75%, 0.60 needs 100%. The risk only returns for a capacity BELOW the floor, so V-22 warns on exactly that. REQ-CAL-04 and REQ-CAL-07 reworded; Config default 0.80 -&gt; 0.60.</t>
+          <t>Applied as REQ-DSH-10. A display rule, not a data change: period_name stays 'Conduct' in the workbook and the screen shows it with its sequence, 'Conduct (1)' and 'Conduct (2)'. Changing the stored name would have broken the weight lookup and V-15.</t>
         </is>
       </c>
       <c r="E69" s="17" t="inlineStr">
@@ -5321,93 +5321,120 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Calculation</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>Re-baseline REQ-NFR-03 to 100 projects and 1,000 people (S2-06).</t>
+          <t>Thresholds stay ABSOLUTE, not relative to capacity_fte (S2-01), and the under-allocation floor moves to 0.60 FTE (S2-05).</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Applied, and it was the most consequential answer in this round. At that volume the person table is 1,000 rows x 60 months = 60,000 cells, and the per-person chart would be 1,000 bars at roughly 1.2px each. Neither survives a naive build, so virtualisation and aggregation became requirements (REQ-DSH-09) rather than optimisations. Priority raised from Should to Must. SUPERSEDED AT R-47, and worth reading as a lesson rather than only as a record: the volume was reasoned about and never measured, the aggregation half was duly built, and the VIRTUALISATION half was recorded as built for five weeks without existing. Measurement then put the rendering budget's crossing point at about 400 people, so REQ-NFR-03 is now 100 projects and 150 people and the virtualisation clause is withdrawn. Priority stays Must.</t>
+          <t>Applied. Taken together these resolve the defect S2-01 was raised about: at a 0.60 floor every capacity in the data can clear it - 1.00 needs 60% utilisation, 0.80 needs 75%, 0.60 needs 100%. The risk only returns for a capacity BELOW the floor, so V-22 warns on exactly that. REQ-CAL-04 and REQ-CAL-07 reworded; Config default 0.80 -&gt; 0.60.</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>Applied; volume superseded at R-47</t>
+          <t>Applied</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Data model</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Split project_type: 'Clinical Trial' becomes 'NewDrug CT' and 'Biosimilar CT'; every clinical trial is one or the other.</t>
+          <t>Re-baseline REQ-NFR-03 to 100 projects and 1,000 people (S2-06).</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Applied. REQ-PRJ-01 and REQ-PRJ-02 reworded. Both new types share the clinical period set and the same derivation - they differ in weights, not shape. RoleFactor and PeriodWeightStandard are now keyed on the type, so the split can carry real differences rather than being only a label. Schema 2 -&gt; 3. All outputs regenerated.</t>
+          <t>Applied, and it was the most consequential answer in this round. At that volume the person table is 1,000 rows x 60 months = 60,000 cells, and the per-person chart would be 1,000 bars at roughly 1.2px each. Neither survives a naive build, so virtualisation and aggregation became requirements (REQ-DSH-09) rather than optimisations. Priority raised from Should to Must. SUPERSEDED AT R-47, and worth reading as a lesson rather than only as a record: the volume was reasoned about and never measured, the aggregation half was duly built, and the VIRTUALISATION half was recorded as built for five weeks without existing. Measurement then put the rendering budget's crossing point at about 400 people, so REQ-NFR-03 is now 100 projects and 150 people and the virtualisation clause is withdrawn. Priority stays Must.</t>
         </is>
       </c>
       <c r="E71" s="17" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied; volume superseded at R-47</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Data model</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>Split project_type: 'Clinical Trial' becomes 'NewDrug CT' and 'Biosimilar CT'; every clinical trial is one or the other.</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Applied. REQ-PRJ-01 and REQ-PRJ-02 reworded. Both new types share the clinical period set and the same derivation - they differ in weights, not shape. RoleFactor and PeriodWeightStandard are now keyed on the type, so the split can carry real differences rather than being only a label. Schema 2 -&gt; 3. All outputs regenerated.</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
           <t>R-04</t>
         </is>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>Data model</t>
         </is>
       </c>
-      <c r="C72" s="11" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>Add at least one free-text note column to every sheet of the source workbook.</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>Applied. Four sheets had none and each gains note_1: Milestone, ProjectPeriod, PeriodWeightStandard, Lists. Six already had one. Source schema version steps 1 -&gt; 2. Note columns are carried through import and export unchanged and never read by the calculation, so the dummy dataset produces identical figures.</t>
         </is>
       </c>
-      <c r="E72" s="17" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>Applied</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>All four are settled. Nothing on this sheet is open, and the plan is final.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>Six engineering decisions - C-06 to C-11 on sheet 05 - were proposed during the review rounds and never explicitly answered. Gate 1 approval of v1.0 confirmed them.</t>
         </is>
@@ -7769,7 +7796,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>R-62, REQ-DSH-20: AN ISSUE A MANAGER HAS REVIEWED IS SHOWN AS REVIEWED. Asked for from the field: a month short of its standard, over it or with nobody on it may be a decision rather than a problem - 'over in the run-up to the interim lock, the sponsor is paying for it' - and drawing those in the same alarm colour as the ones nobody has examined hides the real alarms among them. A new sheet, IssueReview (project_id, month, issue, status, gap_fte, rationale, reviewed_by, reviewed_at), holds one review per project, month and issue; source schema steps 15 to 16. CLICKING AN ISSUE MONTH in Resource by project, or its row in the Standard vs staffed list, opens the month with a Manager review box: a decision ('Confirmed - no issue', 'Accepted', 'To be fixed'), who confirmed it, the reason, and 'Apply to the whole run' for the consecutive months carrying the same issue - or 'Open the project' to change the data instead. The first two CLOSE the issue and need a reason; 'To be fixed' keeps it open with a note. A closed month STAYS MARKED BUT IS DRAWN MUTED, gray, and clicking it shows the decision, who made it, when and why, which can be changed or removed at any time. The counts on the control, the tile and the list are OPEN issues, with the reviewed ones counted apart ('2 reviewed'); the list filters Any review / Open / Reviewed and sorts open issues first, and Show in Resource by project gains 'Reviewed and closed'. A REVIEW COVERS THE FIGURES IT WAS MADE ON: gap_fte records the gap reviewed, and if the month's gap moves, the review no longer closes it - the month is open again, marked 're-check' - and V-40 (new, information) says so; a review of an issue that has gone is kept as history and V-40 says that too. A review is an edit like any other: held until Save, in the change log, exported and read back, and judged identically by the Python reference. A workbook from before schema 16 opens with no reviews (V-09 information). No figure moves; template v1.20, examples v1.22 and v1.14, the small one carrying two accepted months and one to be fixed. Clicking an issue month used to fold its project row open or shut instead - the row's own click came first - and that is fixed. THE STANDARD VS STAFFED LIST IS IN ORDER OF PROJECT ID, THEN MONTH, both ascending (asked for straight after), and lists every month: it was largest gap first and capped at 40, which in project order would have cut whole projects off the end. tools/test_review.py is new: 49 checks, five proved by putting the fault back.</t>
+          <t>R-62, REQ-DSH-20: AN ISSUE A MANAGER HAS REVIEWED IS SHOWN AS REVIEWED. Asked for from the field: a month short of its standard, over it or with nobody on it may be a decision rather than a problem - 'over in the run-up to the interim lock, the sponsor is paying for it' - and drawing those in the same alarm colour as the ones nobody has examined hides the real alarms among them. A new sheet, IssueReview (project_id, month, issue, status, gap_fte, rationale, reviewed_by, reviewed_at), holds one review per project, month and issue; source schema steps 15 to 16. CLICKING AN ISSUE MONTH in Resource by project, or its row in the Standard vs staffed list, opens the month with a Manager review box: a decision ('Confirmed - no issue', 'Accepted', 'To be fixed'), who confirmed it, the reason, and 'Apply to the whole run' for the consecutive months carrying the same issue - or 'Open the project' to change the data instead. The first two CLOSE the issue and need a reason; 'To be fixed' keeps it open with a note. A closed month STAYS MARKED BUT IS DRAWN MUTED, gray, and clicking it shows the decision, who made it, when and why, which can be changed or removed at any time. The counts on the control, the tile and the list are OPEN issues, with the reviewed ones counted apart ('2 reviewed'); the list filters Any review / Open / Reviewed and sorts open issues first, and Show in Resource by project gains 'Reviewed and closed'. A REVIEW COVERS THE FIGURES IT WAS MADE ON: gap_fte records the gap reviewed, and if the month's gap moves, the review no longer closes it - the month is open again, marked 're-check' - and V-40 (new, information) says so; a review of an issue that has gone is kept as history and V-40 says that too. A review is an edit like any other: held until Save, in the change log, exported and read back, and judged identically by the Python reference. A workbook from before schema 16 opens with no reviews (V-09 information). No figure moves; template v1.20, examples v1.22 and v1.14, the small one carrying two accepted months and one to be fixed. Clicking an issue month used to fold its project row open or shut instead - the row's own click came first - and that is fixed. THE STANDARD VS STAFFED LIST IS IN ORDER OF PROJECT ID, THEN MONTH, both ascending (asked for straight after), and lists every month: it was largest gap first and capped at 40, which in project order would have cut whole projects off the end. tools/test_review.py is new: 49 checks, five proved by putting the fault back. R-63 (PYTHON EDITION, desktop plan v1.18): a plan in My plans takes no editing hold and so never times out; a team plan whose hold lapses and is taken over says so in a pop-up that offers to keep your version; and the file window is redrawn - places, a clickable path, type badges, how long ago and date groups, a filter, list or tiles, details, the keyboard, and who saved or is editing a plan. Python edition 1.35.</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
